--- a/Data/Final Pre-Qualification Questionnaire.xlsx
+++ b/Data/Final Pre-Qualification Questionnaire.xlsx
@@ -5,17 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlMufeedM\Desktop\Supplier Regisstration\Mivors-Maaden-Validate Supplier Registeration request LIVE\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlMufeedM\Documents\UiPath\Mivors-Maaden-Validate-Supplier-Registeration-request\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="3" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Material Questions" sheetId="5" r:id="rId1"/>
     <sheet name="Service Questions" sheetId="6" r:id="rId2"/>
     <sheet name="Project" sheetId="7" r:id="rId3"/>
-    <sheet name="Training Questions" sheetId="8" r:id="rId4"/>
+    <sheet name="Training" sheetId="8" r:id="rId4"/>
     <sheet name="SME Questioneries" sheetId="9" r:id="rId5"/>
     <sheet name="Manufacturer Questioneries" sheetId="12" r:id="rId6"/>
     <sheet name="Consultant" sheetId="11" r:id="rId7"/>

--- a/Data/Final Pre-Qualification Questionnaire.xlsx
+++ b/Data/Final Pre-Qualification Questionnaire.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="3" activeTab="3"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="3" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Material Questions" sheetId="5" r:id="rId1"/>
@@ -17,7 +17,7 @@
     <sheet name="Project" sheetId="7" r:id="rId3"/>
     <sheet name="Training" sheetId="8" r:id="rId4"/>
     <sheet name="SME Questioneries" sheetId="9" r:id="rId5"/>
-    <sheet name="Manufacturer Questioneries" sheetId="12" r:id="rId6"/>
+    <sheet name="Manufacturer" sheetId="12" r:id="rId6"/>
     <sheet name="Consultant" sheetId="11" r:id="rId7"/>
     <sheet name="IT and Software Service" sheetId="14" r:id="rId8"/>
     <sheet name="Materials and Service Providers" sheetId="17" r:id="rId9"/>

--- a/Data/Final Pre-Qualification Questionnaire.xlsx
+++ b/Data/Final Pre-Qualification Questionnaire.xlsx
@@ -5,19 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlMufeedM\Documents\UiPath\Mivors-Maaden-Validate-Supplier-Registeration-request\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlMufeedM\Documents\UiPath\Mivors-Maaden-Validate-Supplier-Registeration-request1\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="3" activeTab="3"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="10305" firstSheet="4" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Material Questions" sheetId="5" r:id="rId1"/>
     <sheet name="Service Questions" sheetId="6" r:id="rId2"/>
     <sheet name="Project" sheetId="7" r:id="rId3"/>
     <sheet name="Training" sheetId="8" r:id="rId4"/>
-    <sheet name="SME Questioneries" sheetId="9" r:id="rId5"/>
-    <sheet name="Manufacturer Questioneries" sheetId="12" r:id="rId6"/>
+    <sheet name="SME" sheetId="9" r:id="rId5"/>
+    <sheet name="Manufacturer" sheetId="12" r:id="rId6"/>
     <sheet name="Consultant" sheetId="11" r:id="rId7"/>
     <sheet name="IT and Software Service" sheetId="14" r:id="rId8"/>
     <sheet name="Materials and Service Providers" sheetId="17" r:id="rId9"/>
@@ -1342,7 +1342,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A18"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="177" bestFit="1" customWidth="1"/>
   </cols>
@@ -1352,67 +1352,67 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="15.5">
+    <row r="2" spans="1:1" ht="15">
       <c r="A2" s="9" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="15.5">
+    <row r="3" spans="1:1" ht="15">
       <c r="A3" s="14" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="15.5">
+    <row r="4" spans="1:1" ht="15">
       <c r="A4" s="10" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="15.5">
+    <row r="5" spans="1:1" ht="15">
       <c r="A5" s="9" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="15.5">
+    <row r="6" spans="1:1" ht="15">
       <c r="A6" s="9" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="15.5">
+    <row r="7" spans="1:1" ht="15">
       <c r="A7" s="9" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="15.5">
+    <row r="8" spans="1:1" ht="15">
       <c r="A8" s="8"/>
     </row>
-    <row r="9" spans="1:1" ht="15.5">
+    <row r="9" spans="1:1" ht="15">
       <c r="A9" s="8"/>
     </row>
-    <row r="10" spans="1:1" ht="15.5">
+    <row r="10" spans="1:1" ht="15">
       <c r="A10" s="8"/>
     </row>
-    <row r="11" spans="1:1" ht="15">
+    <row r="11" spans="1:1" ht="15.75">
       <c r="A11" s="7"/>
     </row>
-    <row r="12" spans="1:1" ht="15.5">
+    <row r="12" spans="1:1" ht="15">
       <c r="A12" s="8"/>
     </row>
-    <row r="13" spans="1:1" ht="15.5">
+    <row r="13" spans="1:1" ht="15">
       <c r="A13" s="8"/>
     </row>
-    <row r="14" spans="1:1" ht="15">
+    <row r="14" spans="1:1" ht="15.75">
       <c r="A14" s="7"/>
     </row>
-    <row r="15" spans="1:1" ht="15.5">
+    <row r="15" spans="1:1" ht="15">
       <c r="A15" s="8"/>
     </row>
-    <row r="16" spans="1:1" ht="15.5">
+    <row r="16" spans="1:1" ht="15">
       <c r="A16" s="8"/>
     </row>
-    <row r="17" spans="1:1" ht="15">
+    <row r="17" spans="1:1" ht="15.75">
       <c r="A17" s="7"/>
     </row>
-    <row r="18" spans="1:1" ht="15.5">
+    <row r="18" spans="1:1" ht="15">
       <c r="A18" s="8"/>
     </row>
   </sheetData>
@@ -1426,19 +1426,19 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L10"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="36" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.25" bestFit="1" customWidth="1"/>
     <col min="3" max="5" width="5.75" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="5.75" customWidth="1"/>
-    <col min="7" max="7" width="4.4140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.375" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="5.75" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.4140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="5.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="125.5" thickBot="1">
+    <row r="1" spans="1:12" ht="125.25" thickBot="1">
       <c r="A1" s="17" t="s">
         <v>19</v>
       </c>
@@ -1476,7 +1476,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="16" thickBot="1">
+    <row r="2" spans="1:12" ht="15.75" thickBot="1">
       <c r="A2" s="15" t="s">
         <v>27</v>
       </c>
@@ -1504,7 +1504,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="16" thickBot="1">
+    <row r="3" spans="1:12" ht="15.75" thickBot="1">
       <c r="A3" s="15" t="s">
         <v>28</v>
       </c>
@@ -1520,7 +1520,7 @@
       <c r="K3" s="15"/>
       <c r="L3" s="15"/>
     </row>
-    <row r="4" spans="1:12" ht="16" thickBot="1">
+    <row r="4" spans="1:12" ht="15.75" thickBot="1">
       <c r="A4" s="15" t="s">
         <v>29</v>
       </c>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="L4" s="15"/>
     </row>
-    <row r="5" spans="1:12" ht="16" thickBot="1">
+    <row r="5" spans="1:12" ht="15.75" thickBot="1">
       <c r="A5" s="15" t="s">
         <v>30</v>
       </c>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L5" s="15"/>
     </row>
-    <row r="6" spans="1:12" ht="16" thickBot="1">
+    <row r="6" spans="1:12" ht="15.75" thickBot="1">
       <c r="A6" s="15" t="s">
         <v>32</v>
       </c>
@@ -1600,7 +1600,7 @@
       <c r="K6" s="15"/>
       <c r="L6" s="15"/>
     </row>
-    <row r="7" spans="1:12" ht="16" thickBot="1">
+    <row r="7" spans="1:12" ht="15.75" thickBot="1">
       <c r="A7" s="15" t="s">
         <v>33</v>
       </c>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="L7" s="15"/>
     </row>
-    <row r="8" spans="1:12" ht="16" thickBot="1">
+    <row r="8" spans="1:12" ht="15.75" thickBot="1">
       <c r="A8" s="15" t="s">
         <v>31</v>
       </c>
@@ -1646,7 +1646,7 @@
       <c r="K8" s="15"/>
       <c r="L8" s="15"/>
     </row>
-    <row r="9" spans="1:12" ht="16" thickBot="1">
+    <row r="9" spans="1:12" ht="15.75" thickBot="1">
       <c r="A9" s="15" t="s">
         <v>34</v>
       </c>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="L9" s="15"/>
     </row>
-    <row r="10" spans="1:12" ht="16" thickBot="1">
+    <row r="10" spans="1:12" ht="15.75" thickBot="1">
       <c r="A10" s="15" t="s">
         <v>35</v>
       </c>
@@ -1710,17 +1710,17 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="33.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="17">
+    <row r="1" spans="1:6" ht="17.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1740,7 +1740,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="17.5">
+    <row r="2" spans="1:6" ht="17.25">
       <c r="A2" s="1" t="s">
         <v>15</v>
       </c>
@@ -1760,7 +1760,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="17.5">
+    <row r="3" spans="1:6" ht="17.25">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="17.5">
+    <row r="4" spans="1:6" ht="17.25">
       <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
@@ -1800,7 +1800,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="17.5">
+    <row r="5" spans="1:6" ht="17.25">
       <c r="A5" s="1" t="s">
         <v>17</v>
       </c>
@@ -1820,7 +1820,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="17.5">
+    <row r="6" spans="1:6" ht="17.25">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -1851,12 +1851,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="176" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15.5">
+    <row r="1" spans="1:1" ht="15.75">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1903,13 +1903,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="188.5" customWidth="1"/>
     <col min="2" max="2" width="21.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5">
+    <row r="1" spans="1:2" ht="15.75">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -1987,13 +1987,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="178.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="178.125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="138" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5">
+    <row r="1" spans="1:2" ht="15.75">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -2037,13 +2037,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="191.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5">
+    <row r="1" spans="1:2" ht="15.75">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -2099,13 +2099,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="178.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="178.125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15.5">
+    <row r="1" spans="1:1" ht="15.75">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -2151,12 +2151,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="178.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="178.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15.5">
+    <row r="1" spans="1:1" ht="15.75">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -2197,13 +2197,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="212.4140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="16384" width="9.1640625" style="11"/>
+    <col min="1" max="1" width="212.375" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="9.125" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15.5">
+    <row r="1" spans="1:1" ht="15.75">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -2245,7 +2245,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="108.25" bestFit="1" customWidth="1"/>
   </cols>
